--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -477,16 +477,6 @@
   </si>
   <si>
     <t>Méthode ou technique employée</t>
-  </si>
-  <si>
-    <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.choice[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-sujet-non-humain
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-sujet-non-humain</t>
-  </si>
-  <si>
-    <t>Sujet non humain ou Patient avec sujet non humain</t>
   </si>
   <si>
     <t>fr-lm-resultat-examens-biologie-element-clinique-pertinent.laboratoireExecutant</t>
@@ -831,7 +821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="83.64453125" customWidth="true" bestFit="true"/>
@@ -844,7 +834,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.77734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.8515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3197,7 +3187,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3272,7 +3262,7 @@
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
@@ -3509,13 +3499,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3583,10 +3573,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3597,7 +3587,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3612,10 +3602,10 @@
         <v>80</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3666,118 +3656,18 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-resultat-examens-biologie-element-clinique-pertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
